--- a/Tabelas/tabelas.xlsx
+++ b/Tabelas/tabelas.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1c4728a6baa2a1/Documentos/GitHub/complexidade_terminologica/Tabelas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_FE11B3427502884310ED750BA95A75E66F18A824" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12A5AB4C-FBD0-489D-877E-D8BEDF37F14F}"/>
   <bookViews>
-    <workbookView xWindow="6740" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,385 +14,13 @@
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="122">
-  <si>
-    <t>Cod</t>
-  </si>
-  <si>
-    <t>empresas</t>
-  </si>
-  <si>
-    <t>nomenclatura</t>
-  </si>
-  <si>
-    <t>1.02.01.10.03</t>
-  </si>
-  <si>
-    <t>2.01.05.02.05</t>
-  </si>
-  <si>
-    <t>1.02.01.10.05</t>
-  </si>
-  <si>
-    <t>2.02.02.02.03</t>
-  </si>
-  <si>
-    <t>1.02.01.10.04</t>
-  </si>
-  <si>
-    <t>2.02.02.02.05</t>
-  </si>
-  <si>
-    <t>1.01.08.03.01</t>
-  </si>
-  <si>
-    <t>2.02.02.02.04</t>
-  </si>
-  <si>
-    <t>1.02.01.10.06</t>
-  </si>
-  <si>
-    <t>2.01.05.02.06</t>
-  </si>
-  <si>
-    <t>1.01.08.03.02</t>
-  </si>
-  <si>
-    <t>2.01.05.02.04</t>
-  </si>
-  <si>
-    <t>1.01.08.03.03</t>
-  </si>
-  <si>
-    <t>2.02.02.02.06</t>
-  </si>
-  <si>
-    <t>1.02.01.10.07</t>
-  </si>
-  <si>
-    <t>2.01.05.02.07</t>
-  </si>
-  <si>
-    <t>1.01.08.03.04</t>
-  </si>
-  <si>
-    <t>2.01.05.02.08</t>
-  </si>
-  <si>
-    <t>1.02.04.01.02</t>
-  </si>
-  <si>
-    <t>2.02.02.02.07</t>
-  </si>
-  <si>
-    <t>Terminologia</t>
-  </si>
-  <si>
-    <t>Contas diferentes Ativo</t>
-  </si>
-  <si>
-    <t>Uso Ativo</t>
-  </si>
-  <si>
-    <t>Contas diferentes Passivo</t>
-  </si>
-  <si>
-    <t>Uso Passivo</t>
-  </si>
-  <si>
-    <t>adiantamento a fornecedores</t>
-  </si>
-  <si>
-    <t>adiantamento de clientes</t>
-  </si>
-  <si>
-    <t>adiantamentos a fornecedores</t>
-  </si>
-  <si>
-    <t>adiantamentos de clientes</t>
-  </si>
-  <si>
-    <t>aplicações financeiras</t>
-  </si>
-  <si>
-    <t>arrendamento mercantil</t>
-  </si>
-  <si>
-    <t>arrendamentos a pagar</t>
-  </si>
-  <si>
-    <t>caixa restrito</t>
-  </si>
-  <si>
-    <t>contas a pagar</t>
-  </si>
-  <si>
-    <t>contas a receber</t>
-  </si>
-  <si>
-    <t>créditos com partes relacionadas</t>
-  </si>
-  <si>
-    <t>depósitos judiciais</t>
-  </si>
-  <si>
-    <t>despesas antecipadas</t>
-  </si>
-  <si>
-    <t>dividendos a receber</t>
-  </si>
-  <si>
-    <t>encargos setoriais</t>
-  </si>
-  <si>
-    <t>imposto de renda e contribuição social a recuperar</t>
-  </si>
-  <si>
-    <t>impostos a recuperar</t>
-  </si>
-  <si>
-    <t>impostos e contribuições a recolher</t>
-  </si>
-  <si>
-    <t>instrumentos financeiros derivativos</t>
-  </si>
-  <si>
-    <t>obrigações tributárias</t>
-  </si>
-  <si>
-    <t>outras contas a pagar</t>
-  </si>
-  <si>
-    <t>outras contas a receber</t>
-  </si>
-  <si>
-    <t>outras obrigações</t>
-  </si>
-  <si>
-    <t>outras provisões</t>
-  </si>
-  <si>
-    <t>outros</t>
-  </si>
-  <si>
-    <t>outros ativos</t>
-  </si>
-  <si>
-    <t>outros ativos não circulantes</t>
-  </si>
-  <si>
-    <t>outros créditos</t>
-  </si>
-  <si>
-    <t>outros passivos</t>
-  </si>
-  <si>
-    <t>partes relacionadas</t>
-  </si>
-  <si>
-    <t>passivo de arrendamento</t>
-  </si>
-  <si>
-    <t>passivos de arrendamento</t>
-  </si>
-  <si>
-    <t>receita diferida</t>
-  </si>
-  <si>
-    <t>receitas diferidas</t>
-  </si>
-  <si>
-    <t>tributos a recolher</t>
-  </si>
-  <si>
-    <t>tributos a recuperar</t>
-  </si>
-  <si>
-    <t>títulos e valores mobiliários</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Ativo (1)</t>
-  </si>
-  <si>
-    <t>Ativo (2)</t>
-  </si>
-  <si>
-    <t>Passivo (1)</t>
-  </si>
-  <si>
-    <t>Passivo (2)</t>
-  </si>
-  <si>
-    <t>Qtde de terminologias diferentes</t>
-  </si>
-  <si>
-    <t>Qtde de term. desconsiderando diferenças entre maiúsculo e minúsculo</t>
-  </si>
-  <si>
-    <t>Qtde de term. desconsiderando diferenças de acentuação</t>
-  </si>
-  <si>
-    <t>Qtde de term. desconsiderando diferenças de acentuação e
-          maiúsculo/minúsculo</t>
-  </si>
-  <si>
-    <t>Nível</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Mínimo</t>
-  </si>
-  <si>
-    <t>Máximo</t>
-  </si>
-  <si>
-    <t>Mediana</t>
-  </si>
-  <si>
-    <t>Média Passivo</t>
-  </si>
-  <si>
-    <t>Mínimo Passivo</t>
-  </si>
-  <si>
-    <t>Máximo Passivo</t>
-  </si>
-  <si>
-    <t>Mediana Passivo</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Cod.</t>
-  </si>
-  <si>
-    <t>Empresas</t>
-  </si>
-  <si>
-    <t>Terminologias</t>
-  </si>
-  <si>
-    <t>1.01.02.01</t>
-  </si>
-  <si>
-    <t>Aplicações Financeiras Avaliadas a Valor Justo através do Resultado</t>
-  </si>
-  <si>
-    <t>1.01.02.02</t>
-  </si>
-  <si>
-    <t>Aplicações Financeiras Avaliadas a Valor Justo através de Outros Resultados Abrangentes</t>
-  </si>
-  <si>
-    <t>1.01.02.03</t>
-  </si>
-  <si>
-    <t>Aplicações Financeiras Avaliadas ao Custo Amortizado</t>
-  </si>
-  <si>
-    <t>1.01.03.01</t>
-  </si>
-  <si>
-    <t>Clientes</t>
-  </si>
-  <si>
-    <t>1.01.03.02</t>
-  </si>
-  <si>
-    <t>Outras Contas a Receber</t>
-  </si>
-  <si>
-    <t>2.01.01.01</t>
-  </si>
-  <si>
-    <t>Obrigações Sociais</t>
-  </si>
-  <si>
-    <t>2.01.01.02</t>
-  </si>
-  <si>
-    <t>Obrigações Trabalhistas</t>
-  </si>
-  <si>
-    <t>2.01.02.01</t>
-  </si>
-  <si>
-    <t>Fornecedores Nacionais</t>
-  </si>
-  <si>
-    <t>1.01.02.01.01</t>
-  </si>
-  <si>
-    <t>Títulos para Negociação</t>
-  </si>
-  <si>
-    <t>1.01.02.01.02</t>
-  </si>
-  <si>
-    <t>Títulos Designados a Valor Justo</t>
-  </si>
-  <si>
-    <t>1.02.01.01.01</t>
-  </si>
-  <si>
-    <t>1.02.01.09.01</t>
-  </si>
-  <si>
-    <t>Créditos com Coligadas</t>
-  </si>
-  <si>
-    <t>1.02.01.10.01</t>
-  </si>
-  <si>
-    <t>Ativos Não-Correntes a Venda</t>
-  </si>
-  <si>
-    <t>2.01.03.01.01</t>
-  </si>
-  <si>
-    <t>Imposto de Renda e Contribuição Social a Pagar</t>
-  </si>
-  <si>
-    <t>2.01.04.01.01</t>
-  </si>
-  <si>
-    <t>Em Moeda Nacional</t>
-  </si>
-  <si>
-    <t>2.01.04.01.02</t>
-  </si>
-  <si>
-    <t>Em Moeda Estrangeira</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,21 +68,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -498,7 +112,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -532,7 +146,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -567,10 +180,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -743,33 +355,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>empresas</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>nomenclatura</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cod</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>empresas</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>nomenclatura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1.02.01.10.03</t>
+        </is>
       </c>
       <c r="B2">
         <v>411</v>
@@ -777,8 +403,10 @@
       <c r="C2">
         <v>167</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2.01.05.02.05</t>
+        </is>
       </c>
       <c r="E2">
         <v>412</v>
@@ -787,9 +415,11 @@
         <v>259</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1.02.01.10.05</t>
+        </is>
       </c>
       <c r="B3">
         <v>317</v>
@@ -797,8 +427,10 @@
       <c r="C3">
         <v>162</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.02.02.02.03</t>
+        </is>
       </c>
       <c r="E3">
         <v>415</v>
@@ -807,9 +439,11 @@
         <v>250</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1.02.01.10.04</t>
+        </is>
       </c>
       <c r="B4">
         <v>375</v>
@@ -817,8 +451,10 @@
       <c r="C4">
         <v>161</v>
       </c>
-      <c r="D4" t="s">
-        <v>8</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.02.02.02.05</t>
+        </is>
       </c>
       <c r="E4">
         <v>354</v>
@@ -827,9 +463,11 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1.01.08.03.01</t>
+        </is>
       </c>
       <c r="B5">
         <v>329</v>
@@ -837,8 +475,10 @@
       <c r="C5">
         <v>151</v>
       </c>
-      <c r="D5" t="s">
-        <v>10</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.02.02.02.04</t>
+        </is>
       </c>
       <c r="E5">
         <v>388</v>
@@ -847,9 +487,11 @@
         <v>232</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1.02.01.10.06</t>
+        </is>
       </c>
       <c r="B6">
         <v>225</v>
@@ -857,8 +499,10 @@
       <c r="C6">
         <v>141</v>
       </c>
-      <c r="D6" t="s">
-        <v>12</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2.01.05.02.06</t>
+        </is>
       </c>
       <c r="E6">
         <v>362</v>
@@ -867,9 +511,11 @@
         <v>228</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1.01.08.03.02</t>
+        </is>
       </c>
       <c r="B7">
         <v>315</v>
@@ -877,8 +523,10 @@
       <c r="C7">
         <v>136</v>
       </c>
-      <c r="D7" t="s">
-        <v>14</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.01.05.02.04</t>
+        </is>
       </c>
       <c r="E7">
         <v>431</v>
@@ -887,9 +535,11 @@
         <v>226</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>15</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1.01.08.03.03</t>
+        </is>
       </c>
       <c r="B8">
         <v>223</v>
@@ -897,8 +547,10 @@
       <c r="C8">
         <v>126</v>
       </c>
-      <c r="D8" t="s">
-        <v>16</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.02.02.02.06</t>
+        </is>
       </c>
       <c r="E8">
         <v>305</v>
@@ -907,9 +559,11 @@
         <v>202</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>17</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1.02.01.10.07</t>
+        </is>
       </c>
       <c r="B9">
         <v>145</v>
@@ -917,8 +571,10 @@
       <c r="C9">
         <v>99</v>
       </c>
-      <c r="D9" t="s">
-        <v>18</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.01.05.02.07</t>
+        </is>
       </c>
       <c r="E9">
         <v>295</v>
@@ -927,9 +583,11 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1.01.08.03.04</t>
+        </is>
       </c>
       <c r="B10">
         <v>142</v>
@@ -937,8 +595,10 @@
       <c r="C10">
         <v>96</v>
       </c>
-      <c r="D10" t="s">
-        <v>20</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.01.05.02.08</t>
+        </is>
       </c>
       <c r="E10">
         <v>238</v>
@@ -947,9 +607,11 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>21</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1.02.04.01.02</t>
+        </is>
       </c>
       <c r="B11">
         <v>229</v>
@@ -957,8 +619,10 @@
       <c r="C11">
         <v>81</v>
       </c>
-      <c r="D11" t="s">
-        <v>22</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.02.02.02.07</t>
+        </is>
       </c>
       <c r="E11">
         <v>229</v>
@@ -973,34 +637,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="49.7109375" customWidth="1"/>
-    <col min="2" max="5" width="17.85546875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>28</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Terminologia</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contas diferentes Ativo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Uso Ativo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Contas diferentes Passivo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Uso Passivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adiantamento a fornecedores</t>
+        </is>
       </c>
       <c r="B2">
         <v>31</v>
@@ -1009,9 +681,11 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>29</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adiantamento de clientes</t>
+        </is>
       </c>
       <c r="D3">
         <v>34</v>
@@ -1020,9 +694,11 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>30</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adiantamentos a fornecedores</t>
+        </is>
       </c>
       <c r="B4">
         <v>23</v>
@@ -1031,9 +707,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>31</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adiantamentos de clientes</t>
+        </is>
       </c>
       <c r="D5">
         <v>22</v>
@@ -1042,9 +720,11 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>32</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aplicações financeiras</t>
+        </is>
       </c>
       <c r="B6">
         <v>23</v>
@@ -1053,9 +733,11 @@
         <v>509</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>33</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>arrendamento mercantil</t>
+        </is>
       </c>
       <c r="D7">
         <v>30</v>
@@ -1064,9 +746,11 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>34</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>arrendamentos a pagar</t>
+        </is>
       </c>
       <c r="D8">
         <v>25</v>
@@ -1075,9 +759,11 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>35</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>caixa restrito</t>
+        </is>
       </c>
       <c r="B9">
         <v>32</v>
@@ -1086,9 +772,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>36</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>contas a pagar</t>
+        </is>
       </c>
       <c r="D10">
         <v>21</v>
@@ -1097,9 +785,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>37</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>contas a receber</t>
+        </is>
       </c>
       <c r="B11">
         <v>19</v>
@@ -1108,9 +798,11 @@
         <v>932</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>38</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>créditos com partes relacionadas</t>
+        </is>
       </c>
       <c r="B12">
         <v>17</v>
@@ -1119,9 +811,11 @@
         <v>475</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>39</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>depósitos judiciais</t>
+        </is>
       </c>
       <c r="B13">
         <v>27</v>
@@ -1130,9 +824,11 @@
         <v>247</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>40</v>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>despesas antecipadas</t>
+        </is>
       </c>
       <c r="B14">
         <v>18</v>
@@ -1141,9 +837,11 @@
         <v>935</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>41</v>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dividendos a receber</t>
+        </is>
       </c>
       <c r="B15">
         <v>28</v>
@@ -1152,9 +850,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>42</v>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>encargos setoriais</t>
+        </is>
       </c>
       <c r="D16">
         <v>21</v>
@@ -1163,9 +863,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>43</v>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>imposto de renda e contribuição social a recuperar</t>
+        </is>
       </c>
       <c r="B17">
         <v>28</v>
@@ -1174,9 +876,11 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>44</v>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>impostos a recuperar</t>
+        </is>
       </c>
       <c r="B18">
         <v>31</v>
@@ -1185,9 +889,11 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>45</v>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>impostos e contribuições a recolher</t>
+        </is>
       </c>
       <c r="D19">
         <v>25</v>
@@ -1196,9 +902,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>46</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>instrumentos financeiros derivativos</t>
+        </is>
       </c>
       <c r="B20">
         <v>48</v>
@@ -1213,9 +921,11 @@
         <v>226</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>47</v>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>obrigações tributárias</t>
+        </is>
       </c>
       <c r="D21">
         <v>27</v>
@@ -1224,9 +934,11 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>48</v>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>outras contas a pagar</t>
+        </is>
       </c>
       <c r="D22">
         <v>55</v>
@@ -1235,9 +947,11 @@
         <v>237</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>49</v>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>outras contas a receber</t>
+        </is>
       </c>
       <c r="B23">
         <v>35</v>
@@ -1246,9 +960,11 @@
         <v>948</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>50</v>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>outras obrigações</t>
+        </is>
       </c>
       <c r="D24">
         <v>45</v>
@@ -1257,9 +973,11 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>51</v>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>outras provisões</t>
+        </is>
       </c>
       <c r="D25">
         <v>22</v>
@@ -1268,9 +986,11 @@
         <v>939</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>52</v>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
       </c>
       <c r="B26">
         <v>40</v>
@@ -1285,9 +1005,11 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>53</v>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>outros ativos</t>
+        </is>
       </c>
       <c r="B27">
         <v>40</v>
@@ -1296,9 +1018,11 @@
         <v>198</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>54</v>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>outros ativos não circulantes</t>
+        </is>
       </c>
       <c r="B28">
         <v>20</v>
@@ -1307,9 +1031,11 @@
         <v>491</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>55</v>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>outros créditos</t>
+        </is>
       </c>
       <c r="B29">
         <v>50</v>
@@ -1318,9 +1044,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>56</v>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>outros passivos</t>
+        </is>
       </c>
       <c r="D30">
         <v>46</v>
@@ -1329,9 +1057,11 @@
         <v>152</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>57</v>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>partes relacionadas</t>
+        </is>
       </c>
       <c r="B31">
         <v>40</v>
@@ -1346,9 +1076,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>58</v>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>passivo de arrendamento</t>
+        </is>
       </c>
       <c r="D32">
         <v>45</v>
@@ -1357,9 +1089,11 @@
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>59</v>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>passivos de arrendamento</t>
+        </is>
       </c>
       <c r="D33">
         <v>24</v>
@@ -1368,9 +1102,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>60</v>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>receita diferida</t>
+        </is>
       </c>
       <c r="D34">
         <v>20</v>
@@ -1379,9 +1115,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>61</v>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>receitas diferidas</t>
+        </is>
       </c>
       <c r="D35">
         <v>25</v>
@@ -1390,9 +1128,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>62</v>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>tributos a recolher</t>
+        </is>
       </c>
       <c r="D36">
         <v>22</v>
@@ -1401,9 +1141,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>63</v>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>tributos a recuperar</t>
+        </is>
       </c>
       <c r="B37">
         <v>23</v>
@@ -1412,9 +1154,11 @@
         <v>600</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>64</v>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>títulos e valores mobiliários</t>
+        </is>
       </c>
       <c r="B38">
         <v>32</v>
@@ -1429,30 +1173,42 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>70</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ativo (1)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ativo (2)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Passivo (1)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Passivo (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Qtde de terminologias diferentes</t>
+        </is>
       </c>
       <c r="B2">
         <v>1727</v>
@@ -1467,9 +1223,11 @@
         <v>5223</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>71</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Qtde de term. desconsiderando diferenças entre maiúsculo e minúsculo</t>
+        </is>
       </c>
       <c r="B3">
         <v>1686</v>
@@ -1484,9 +1242,11 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>72</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Qtde de term. desconsiderando diferenças de acentuação</t>
+        </is>
       </c>
       <c r="B4">
         <v>1472</v>
@@ -1501,9 +1261,12 @@
         <v>4734</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>73</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Qtde de term. desconsiderando diferenças de acentuação e
+          maiúsculo/minúsculo</t>
+        </is>
       </c>
       <c r="B5">
         <v>1428</v>
@@ -1524,42 +1287,62 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>83</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nível</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Máximo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mediana</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Média Passivo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mínimo Passivo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Máximo Passivo</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Mediana Passivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1586,9 +1369,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>84</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1615,9 +1400,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>85</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1644,9 +1431,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>86</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5">
         <v>4.78</v>
@@ -1673,12 +1462,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>87</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6">
-        <v>17.940000000000001</v>
+        <v>17.94</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1708,107 +1499,1075 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C71"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>91</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cod.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Empresas</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Terminologias</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1.01.02.01</t>
+        </is>
       </c>
       <c r="B2">
         <v>450</v>
       </c>
-      <c r="C2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>93</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Aplicações Financeiras Avaliadas a Valor Justo através do Resultado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1.01.02.02</t>
+        </is>
       </c>
       <c r="B3">
         <v>450</v>
       </c>
-      <c r="C3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>95</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Aplicações Financeiras Avaliadas a Valor Justo através de Outros Resultados Abrangentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1.01.02.03</t>
+        </is>
       </c>
       <c r="B4">
         <v>450</v>
       </c>
-      <c r="C4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>97</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Aplicações Financeiras Avaliadas ao Custo Amortizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1.01.03.01</t>
+        </is>
       </c>
       <c r="B5">
         <v>450</v>
       </c>
-      <c r="C5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>99</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Clientes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1.01.03.02</t>
+        </is>
       </c>
       <c r="B6">
         <v>450</v>
       </c>
-      <c r="C6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>101</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Outras Contas a Receber</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1.01.06.01</t>
+        </is>
       </c>
       <c r="B7">
         <v>450</v>
       </c>
-      <c r="C7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>103</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tributos Correntes a Recuperar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1.01.08.01</t>
+        </is>
       </c>
       <c r="B8">
         <v>450</v>
       </c>
-      <c r="C8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>105</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ativos Não-Correntes a Venda</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1.01.08.02</t>
+        </is>
       </c>
       <c r="B9">
         <v>450</v>
       </c>
-      <c r="C9" t="s">
-        <v>106</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ativos de Operações Descontinuadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1.01.08.03</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>450</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1.02.01.01</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>450</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Aplicações Financeiras Avaliadas a Valor Justo através do Resultado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1.02.01.02</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>450</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Aplicações Financeiras Avaliadas a Valor Justo através de Outros Resultados Abrangentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1.02.01.03</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>450</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Aplicações Financeiras Avaliadas ao Custo Amortizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1.02.01.04</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>450</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Contas a Receber</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1.02.01.05</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>450</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Estoques</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1.02.01.06</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>450</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ativos Biológicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1.02.01.07</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>450</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tributos Diferidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1.02.01.08</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>450</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Despesas Antecipadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1.02.01.09</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>450</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Créditos com Partes Relacionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1.02.01.10</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>450</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Outros Ativos Não Circulantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1.02.02.01</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>450</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Participações Societárias</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1.02.02.02</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>450</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Propriedades para Investimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1.02.03.01</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>450</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Imobilizado em Operação</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1.02.03.02</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>450</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Direito de Uso em Arrendamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1.02.03.03</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>450</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Imobilizado em Andamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1.02.04.01</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>450</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Intangíveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1.02.04.02</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>450</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2.01.01.01</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>450</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Obrigações Sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2.01.01.02</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>450</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Obrigações Trabalhistas</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2.01.02.01</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>450</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Fornecedores Nacionais</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2.01.02.02</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>450</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Fornecedores Estrangeiros</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2.01.03.01</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>450</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Obrigações Fiscais Federais</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2.01.03.02</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>450</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Obrigações Fiscais Estaduais</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2.01.03.03</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>450</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Obrigações Fiscais Municipais</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2.01.04.01</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>450</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Empréstimos e Financiamentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2.01.04.02</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>450</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Debêntures</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2.01.04.03</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>450</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Financiamento por Arrendamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2.01.05.01</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>450</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Passivos com Partes Relacionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2.01.05.02</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>450</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2.01.06.01</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>450</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Provisões Fiscais Previdenciárias Trabalhistas e Cíveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2.01.06.02</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>450</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Outras Provisões</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2.01.07.01</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>450</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Passivos sobre Ativos Não-Correntes a Venda</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2.01.07.02</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>450</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Passivos sobre Ativos de Operações Descontinuadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2.02.01.01</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>450</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Empréstimos e Financiamentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2.02.01.02</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>450</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Debêntures</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2.02.01.03</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>450</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Financiamento por Arrendamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2.02.02.01</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>450</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Passivos com Partes Relacionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2.02.02.02</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>450</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2.02.03.01</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>450</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Imposto de Renda e Contribuição Social Diferidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2.02.04.01</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>450</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Provisões Fiscais Previdenciárias Trabalhistas e Cíveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2.02.04.02</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>450</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Outras Provisões</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2.02.05.01</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>450</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Passivos sobre Ativos Não-Correntes a Venda</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2.02.05.02</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>450</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Passivos sobre Ativos de Operações Descontinuadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2.02.06.01</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>450</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Lucros a Apropriar</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2.02.06.02</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>450</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Receitas a Apropriar</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2.02.06.03</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>450</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Subvenções de Investimento a Apropriar</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2.03.02.01</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>450</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ágio na Emissão de Ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2.03.02.02</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>450</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Reserva Especial de Ágio na Incorporação</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2.03.02.03</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>450</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Alienação de Bônus de Subscrição</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2.03.02.04</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>450</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Opções Outorgadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2.03.02.05</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>450</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ações em Tesouraria</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2.03.02.06</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>450</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Adiantamento para Futuro Aumento de Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2.03.04.01</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>450</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Reserva Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2.03.04.02</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>450</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Reserva Estatutária</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2.03.04.03</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>450</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Reserva para Contingências</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2.03.04.04</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>450</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Reserva de Lucros a Realizar</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2.03.04.05</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>450</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Reserva de Retenção de Lucros</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2.03.04.06</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>450</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Reserva Especial para Dividendos Não Distribuídos</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2.03.04.07</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>450</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Reserva de Incentivos Fiscais</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2.03.04.08</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>450</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Dividendo Adicional Proposto</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2.03.04.09</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>450</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ações em Tesouraria</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1817,107 +2576,625 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>107</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cod.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Empresas</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Terminologias</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1.01.02.01.01</t>
+        </is>
       </c>
       <c r="B2">
         <v>450</v>
       </c>
-      <c r="C2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>109</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Títulos para Negociação</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1.01.02.01.02</t>
+        </is>
       </c>
       <c r="B3">
         <v>450</v>
       </c>
-      <c r="C3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>111</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Títulos Designados a Valor Justo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1.02.01.01.01</t>
+        </is>
       </c>
       <c r="B4">
         <v>450</v>
       </c>
-      <c r="C4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>112</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Títulos Designados a Valor Justo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1.02.01.09.01</t>
+        </is>
       </c>
       <c r="B5">
         <v>450</v>
       </c>
-      <c r="C5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>114</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Créditos com Coligadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1.02.01.10.01</t>
+        </is>
       </c>
       <c r="B6">
         <v>450</v>
       </c>
-      <c r="C6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>116</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ativos Não-Correntes a Venda</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1.02.01.10.02</t>
+        </is>
       </c>
       <c r="B7">
         <v>450</v>
       </c>
-      <c r="C7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>118</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ativos de Operações Descontinuadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1.02.02.01.01</t>
+        </is>
       </c>
       <c r="B8">
         <v>450</v>
       </c>
-      <c r="C8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>120</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Participações em Coligadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1.02.02.01.04</t>
+        </is>
       </c>
       <c r="B9">
         <v>450</v>
       </c>
-      <c r="C9" t="s">
-        <v>121</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Participações em Controladas em Conjunto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1.02.02.01.05</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>450</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Outros Investimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1.02.04.01.01</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>450</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Contrato de Concessão</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2.01.03.01.01</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>450</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Imposto de Renda e Contribuição Social a Pagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2.01.04.01.01</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>450</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Em Moeda Nacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2.01.04.01.02</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>450</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Em Moeda Estrangeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2.01.05.01.01</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>450</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Débitos com Coligadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2.01.05.01.03</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>450</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Débitos com Controladores</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2.01.05.01.04</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>450</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Débitos com Outras Partes Relacionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2.01.05.02.01</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>450</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dividendos e JCP a Pagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2.01.05.02.02</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>450</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Dividendo Mínimo Obrigatório a Pagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2.01.05.02.03</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>450</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Obrigações por Pagamentos Baseados em Ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2.01.06.01.01</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>450</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Provisões Fiscais</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2.01.06.01.02</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>450</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Provisões Previdenciárias e Trabalhistas</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2.01.06.01.03</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>450</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Provisões para Benefícios a Empregados</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2.01.06.01.04</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>450</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Provisões Cíveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2.01.06.02.01</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>450</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Provisões para Garantias</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2.01.06.02.02</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>450</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Provisões para Reestruturação</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2.01.06.02.03</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>450</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Provisões para Passivos Ambientais e de Desativação</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2.02.01.01.01</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>450</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Em Moeda Nacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2.02.01.01.02</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>450</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Em Moeda Estrangeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2.02.02.01.01</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>450</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Débitos com Coligadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2.02.02.01.03</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>450</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Débitos com Controladores</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2.02.02.01.04</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>450</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Débitos com Outras Partes Relacionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2.02.02.02.01</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>450</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Obrigações por Pagamentos Baseados em Ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2.02.02.02.02</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>450</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Adiantamento para Futuro Aumento de Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2.02.04.01.01</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>450</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Provisões Fiscais</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2.02.04.01.02</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>450</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Provisões Previdenciárias e Trabalhistas</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2.02.04.01.03</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>450</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Provisões para Benefícios a Empregados</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2.02.04.01.04</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>450</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Provisões Cíveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2.02.04.02.01</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>450</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Provisões para Garantias</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2.02.04.02.02</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>450</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Provisões para Reestruturação</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2.02.04.02.03</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>450</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Provisões para Passivos Ambientais e de Desativação</t>
+        </is>
       </c>
     </row>
   </sheetData>
